--- a/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
@@ -608,6 +608,9 @@
       <c r="C21" t="str">
         <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -666,7 +669,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010106102010201010102015101055100</v>
+        <v>02010101061020102010101020151010551020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,9 +612,92 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>5</v>
+      </c>
+      <c r="C24" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>6</v>
+      </c>
+      <c r="C25" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>625_多丁紫蝴蝶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -669,7 +752,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02010101061020102010101020151010551020</v>
+        <v>020101010610201020101010201510105510202010201055105210</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
@@ -694,6 +694,9 @@
       <c r="C31" t="str">
         <v>586_洋牡丹白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -752,7 +755,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020101010610201020101010201510105510202010201055105210</v>
+        <v>0201010106102010201010102015101055102020102010551052111</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-18.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L34"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -698,9 +698,34 @@
         <v>11</v>
       </c>
     </row>
+    <row r="32" xml:space="preserve">
+      <c r="C32" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F33" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>48_香格里拉_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L34"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -755,7 +780,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0201010106102010201010102015101055102020102010551052111</v>
+        <v>0201010106102010201010102015101055102020102010551052111201510</v>
       </c>
     </row>
   </sheetData>
